--- a/Team-Data/2007-08/12-16-2007-08.xlsx
+++ b/Team-Data/2007-08/12-16-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-1.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF2" t="n">
         <v>14</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
@@ -784,7 +851,7 @@
         <v>14</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
         <v>22</v>
@@ -793,22 +860,22 @@
         <v>25</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY2" t="n">
         <v>22</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB2" t="n">
         <v>27</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.909</v>
+        <v>0.905</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
@@ -870,37 +937,37 @@
         <v>7.4</v>
       </c>
       <c r="M3" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N3" t="n">
         <v>0.383</v>
       </c>
       <c r="O3" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="P3" t="n">
-        <v>27.7</v>
+        <v>28.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.778</v>
+        <v>0.784</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T3" t="n">
-        <v>41.8</v>
+        <v>42.1</v>
       </c>
       <c r="U3" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V3" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="W3" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="X3" t="n">
         <v>4.4</v>
@@ -909,19 +976,19 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.7</v>
+        <v>101.2</v>
       </c>
       <c r="AC3" t="n">
         <v>14.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,37 +1012,37 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM3" t="n">
         <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP3" t="n">
         <v>7</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-6.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
         <v>25</v>
@@ -1133,7 +1200,7 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
         <v>22</v>
@@ -1157,16 +1224,16 @@
         <v>26</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
         <v>5</v>
@@ -1348,7 +1415,7 @@
         <v>16</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ5" t="n">
         <v>15</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1534,22 @@
         <v>-4.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
         <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
         <v>19</v>
       </c>
       <c r="AH6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
@@ -1491,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM6" t="n">
         <v>9</v>
@@ -1506,7 +1573,7 @@
         <v>20</v>
       </c>
       <c r="AQ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR6" t="n">
         <v>11</v>
@@ -1521,16 +1588,16 @@
         <v>27</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>15</v>
       </c>
       <c r="AY6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ6" t="n">
         <v>24</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
         <v>6</v>
@@ -1661,7 +1728,7 @@
         <v>6</v>
       </c>
       <c r="AH7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI7" t="n">
         <v>13</v>
@@ -1670,7 +1737,7 @@
         <v>24</v>
       </c>
       <c r="AK7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL7" t="n">
         <v>17</v>
@@ -1691,13 +1758,13 @@
         <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
         <v>13</v>
       </c>
       <c r="AT7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU7" t="n">
         <v>19</v>
@@ -1706,7 +1773,7 @@
         <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
         <v>10</v>
@@ -1724,7 +1791,7 @@
         <v>10</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" t="n">
-        <v>0.583</v>
+        <v>0.609</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
@@ -1771,55 +1838,55 @@
         <v>38.5</v>
       </c>
       <c r="J8" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
         <v>18.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O8" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R8" t="n">
         <v>10.7</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>43.2</v>
+        <v>43.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="V8" t="n">
-        <v>16.5</v>
+        <v>16.7</v>
       </c>
       <c r="W8" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="X8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA8" t="n">
         <v>24.8</v>
@@ -1828,19 +1895,19 @@
         <v>106.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1876,7 +1943,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
         <v>8</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -1935,133 +2002,133 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.708</v>
+        <v>0.696</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>37.5</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
         <v>80</v>
       </c>
       <c r="K9" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L9" t="n">
         <v>5.5</v>
       </c>
       <c r="M9" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.345</v>
+        <v>0.342</v>
       </c>
       <c r="O9" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P9" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.752</v>
+        <v>0.749</v>
       </c>
       <c r="R9" t="n">
         <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="T9" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="U9" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V9" t="n">
         <v>11.8</v>
       </c>
       <c r="W9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z9" t="n">
         <v>20.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
         <v>3</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
         <v>20</v>
       </c>
       <c r="AN9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AR9" t="n">
         <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU9" t="n">
         <v>4</v>
@@ -2073,13 +2140,13 @@
         <v>24</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA9" t="n">
         <v>22</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -2117,97 +2184,97 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
         <v>13</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>0.542</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>40.2</v>
+        <v>40.5</v>
       </c>
       <c r="J10" t="n">
-        <v>90.2</v>
+        <v>90.7</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L10" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.349</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.72</v>
+        <v>0.722</v>
       </c>
       <c r="R10" t="n">
         <v>13</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8</v>
+        <v>30.3</v>
       </c>
       <c r="T10" t="n">
-        <v>42.8</v>
+        <v>43.3</v>
       </c>
       <c r="U10" t="n">
         <v>22.7</v>
       </c>
       <c r="V10" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="W10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AA10" t="n">
         <v>21.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.1</v>
+        <v>109</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG10" t="n">
         <v>11</v>
       </c>
-      <c r="AG10" t="n">
-        <v>13</v>
-      </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2225,25 +2292,25 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
         <v>17</v>
       </c>
       <c r="AP10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR10" t="n">
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>9</v>
@@ -2255,10 +2322,10 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ10" t="n">
         <v>25</v>
@@ -2270,7 +2337,7 @@
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2392,7 +2459,7 @@
         <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="n">
         <v>15</v>
@@ -2440,7 +2507,7 @@
         <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>11</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-1.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>14</v>
@@ -2571,10 +2638,10 @@
         <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
         <v>2</v>
@@ -2589,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>14</v>
@@ -2598,19 +2665,19 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
       </c>
       <c r="AS12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
         <v>22</v>
@@ -2619,7 +2686,7 @@
         <v>12</v>
       </c>
       <c r="AX12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" t="n">
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.391</v>
+        <v>0.409</v>
       </c>
       <c r="H13" t="n">
         <v>48</v>
@@ -2681,73 +2748,73 @@
         <v>33.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="M13" t="n">
-        <v>15.3</v>
+        <v>15.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
         <v>22.4</v>
       </c>
       <c r="P13" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.785</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>32.4</v>
+        <v>32.7</v>
       </c>
       <c r="T13" t="n">
         <v>42.4</v>
       </c>
       <c r="U13" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V13" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y13" t="n">
         <v>5.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.4</v>
+        <v>-3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG13" t="n">
         <v>22</v>
@@ -2765,13 +2832,13 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO13" t="n">
         <v>4</v>
@@ -2783,7 +2850,7 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
         <v>7</v>
@@ -2795,19 +2862,19 @@
         <v>17</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -2845,100 +2912,100 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.609</v>
+        <v>0.591</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.471</v>
+        <v>0.468</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O14" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="P14" t="n">
-        <v>29.8</v>
+        <v>30.2</v>
       </c>
       <c r="Q14" t="n">
         <v>0.768</v>
       </c>
       <c r="R14" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="S14" t="n">
-        <v>34</v>
+        <v>33.9</v>
       </c>
       <c r="T14" t="n">
         <v>44.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W14" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y14" t="n">
         <v>5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="Z14" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.1</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ14" t="n">
         <v>11</v>
@@ -2947,7 +3014,7 @@
         <v>5</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>7</v>
@@ -2974,10 +3041,10 @@
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW14" t="n">
         <v>5</v>
@@ -2986,19 +3053,19 @@
         <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ14" t="n">
         <v>19</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3135,7 +3202,7 @@
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3147,13 +3214,13 @@
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
         <v>9</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
         <v>15</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>29</v>
@@ -3302,13 +3369,13 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>26</v>
@@ -3329,7 +3396,7 @@
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS16" t="n">
         <v>17</v>
@@ -3353,7 +3420,7 @@
         <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>18</v>
@@ -3541,7 +3608,7 @@
         <v>13</v>
       </c>
       <c r="BB17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>15</v>
       </c>
       <c r="AJ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3711,7 +3778,7 @@
         <v>15</v>
       </c>
       <c r="AX18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY18" t="n">
         <v>24</v>
@@ -3720,7 +3787,7 @@
         <v>28</v>
       </c>
       <c r="BA18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BB18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-5.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3878,7 +3945,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT19" t="n">
         <v>26</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>7</v>
@@ -4039,7 +4106,7 @@
         <v>24</v>
       </c>
       <c r="AL20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM20" t="n">
         <v>8</v>
@@ -4063,7 +4130,7 @@
         <v>10</v>
       </c>
       <c r="AT20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
         <v>22</v>
@@ -4090,7 +4157,7 @@
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-8</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4245,13 +4312,13 @@
         <v>27</v>
       </c>
       <c r="AT21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW21" t="n">
         <v>23</v>
@@ -4263,7 +4330,7 @@
         <v>30</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
         <v>12</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
@@ -4454,7 +4521,7 @@
         <v>7</v>
       </c>
       <c r="BC22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4561,28 +4628,28 @@
         <v>-0.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>18</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
         <v>19</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ23" t="n">
         <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
@@ -4606,7 +4673,7 @@
         <v>3</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT23" t="n">
         <v>13</v>
@@ -4621,10 +4688,10 @@
         <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4806,7 +4873,7 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>1</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -4847,106 +4914,106 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5</v>
+        <v>0.478</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="J25" t="n">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0.465</v>
+        <v>0.461</v>
       </c>
       <c r="L25" t="n">
         <v>5.9</v>
       </c>
       <c r="M25" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N25" t="n">
         <v>0.376</v>
       </c>
       <c r="O25" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="P25" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="Q25" t="n">
         <v>0.75</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="T25" t="n">
-        <v>38.9</v>
+        <v>38.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V25" t="n">
         <v>15.1</v>
       </c>
       <c r="W25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>95.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
       <c r="AD25" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
         <v>14</v>
       </c>
       <c r="AG25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AJ25" t="n">
         <v>27</v>
       </c>
       <c r="AK25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL25" t="n">
         <v>16</v>
@@ -4964,13 +5031,13 @@
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>30</v>
@@ -4982,22 +5049,22 @@
         <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BB25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>-3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>22</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5128,13 +5195,13 @@
         <v>23</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL26" t="n">
         <v>22</v>
       </c>
       <c r="AM26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN26" t="n">
         <v>17</v>
@@ -5143,7 +5210,7 @@
         <v>5</v>
       </c>
       <c r="AP26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT26" t="n">
         <v>28</v>
@@ -5170,7 +5237,7 @@
         <v>29</v>
       </c>
       <c r="AY26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ26" t="n">
         <v>23</v>
@@ -5179,7 +5246,7 @@
         <v>3</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>7.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -5331,7 +5398,7 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
@@ -5340,7 +5407,7 @@
         <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5553,7 @@
         <v>12</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>28</v>
       </c>
       <c r="AN28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO28" t="n">
         <v>13</v>
@@ -5537,13 +5604,13 @@
         <v>21</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
       </c>
       <c r="BB28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>28</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -5575,67 +5642,67 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
         <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.583</v>
       </c>
       <c r="H29" t="n">
         <v>48.2</v>
       </c>
       <c r="I29" t="n">
-        <v>37.1</v>
+        <v>37.5</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L29" t="n">
         <v>8.1</v>
       </c>
       <c r="M29" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.433</v>
+        <v>0.435</v>
       </c>
       <c r="O29" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="P29" t="n">
         <v>19.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.824</v>
+        <v>0.828</v>
       </c>
       <c r="R29" t="n">
         <v>10.4</v>
       </c>
       <c r="S29" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U29" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="V29" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="W29" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y29" t="n">
         <v>4.9</v>
@@ -5647,34 +5714,34 @@
         <v>17.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>8</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL29" t="n">
         <v>6</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5716,19 +5783,19 @@
         <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC29" t="n">
         <v>9</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -5841,10 +5908,10 @@
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>21</v>
@@ -5868,19 +5935,19 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP30" t="n">
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>14</v>
@@ -5904,7 +5971,7 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
@@ -6017,16 +6084,16 @@
         <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
@@ -6038,7 +6105,7 @@
         <v>7</v>
       </c>
       <c r="AK31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,13 +6114,13 @@
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO31" t="n">
         <v>12</v>
       </c>
       <c r="AP31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" t="n">
         <v>4</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-16-2007-08</t>
+          <t>2007-12-16</t>
         </is>
       </c>
     </row>
